--- a/data/trans_orig/IP15-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP15-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16487</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29130</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33992</t>
+          <t>32415</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52131</t>
+          <t>51648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61737</t>
+          <t>61360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74380</t>
+          <t>74821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59139</t>
+          <t>59285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72441</t>
+          <t>72085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125581</t>
+          <t>126064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143720</t>
+          <t>145297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>68771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93635</t>
+          <t>94194</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74991</t>
+          <t>74998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101290</t>
+          <t>101778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149832</t>
+          <t>149986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>188551</t>
+          <t>187636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>322452</t>
+          <t>321893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>347477</t>
+          <t>347316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>375701</t>
+          <t>375213</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>402000</t>
+          <t>401993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704527</t>
+          <t>705442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743246</t>
+          <t>743092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>30968</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28028</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44166</t>
+          <t>44953</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47754</t>
+          <t>47073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69249</t>
+          <t>70351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143831</t>
+          <t>143098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157862</t>
+          <t>157984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113972</t>
+          <t>113185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130110</t>
+          <t>130694</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>262956</t>
+          <t>261854</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284451</t>
+          <t>285132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110980</t>
+          <t>110452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142532</t>
+          <t>142934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126171</t>
+          <t>127312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>163076</t>
+          <t>160443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244929</t>
+          <t>246113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>290609</t>
+          <t>294352</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>538489</t>
+          <t>538087</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>570041</t>
+          <t>570569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>558898</t>
+          <t>561531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>595803</t>
+          <t>594662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1112386</t>
+          <t>1108643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1158066</t>
+          <t>1156882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>30835</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25105</t>
+          <t>25153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51849</t>
+          <t>52728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61390</t>
+          <t>61534</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75548</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>61039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74258</t>
+          <t>73943</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126712</t>
+          <t>125833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146139</t>
+          <t>145459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74408</t>
+          <t>75262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103148</t>
+          <t>104555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85629</t>
+          <t>87339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116140</t>
+          <t>118317</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>168831</t>
+          <t>170822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>210587</t>
+          <t>208705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349062</t>
+          <t>347655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377802</t>
+          <t>376948</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>378306</t>
+          <t>376129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>408817</t>
+          <t>407107</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736069</t>
+          <t>737951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>777825</t>
+          <t>775834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28001</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45936</t>
+          <t>45297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49106</t>
+          <t>49854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63224</t>
+          <t>63368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89028</t>
+          <t>88573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120876</t>
+          <t>121515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138811</t>
+          <t>138957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121623</t>
+          <t>120875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140030</t>
+          <t>139540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248513</t>
+          <t>248968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>274317</t>
+          <t>274173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130280</t>
+          <t>130633</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167322</t>
+          <t>166963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141604</t>
+          <t>142070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178241</t>
+          <t>176875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279691</t>
+          <t>278474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>334227</t>
+          <t>331695</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>544069</t>
+          <t>544428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>581111</t>
+          <t>580758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>573126</t>
+          <t>574492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609763</t>
+          <t>609297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1128531</t>
+          <t>1131063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1183067</t>
+          <t>1184284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10804</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21995</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37383</t>
+          <t>37744</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48691</t>
+          <t>48574</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54302</t>
+          <t>54727</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63615</t>
+          <t>64249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94766</t>
+          <t>94570</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109835</t>
+          <t>109996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70935</t>
+          <t>69872</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96893</t>
+          <t>95968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71737</t>
+          <t>72523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99388</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>148804</t>
+          <t>150491</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189731</t>
+          <t>188253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375397</t>
+          <t>376322</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401355</t>
+          <t>402418</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389347</t>
+          <t>388940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>416998</t>
+          <t>416212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771294</t>
+          <t>772772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>812221</t>
+          <t>810534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21210</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37718</t>
+          <t>37507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46939</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69182</t>
+          <t>71573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135583</t>
+          <t>135478</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151849</t>
+          <t>150642</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149777</t>
+          <t>149988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166285</t>
+          <t>166383</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291015</t>
+          <t>288624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313258</t>
+          <t>312317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111129</t>
+          <t>111243</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144884</t>
+          <t>143709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107274</t>
+          <t>108085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142274</t>
+          <t>141931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228851</t>
+          <t>227717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273319</t>
+          <t>273513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>559487</t>
+          <t>560662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>593242</t>
+          <t>593128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>602570</t>
+          <t>602913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>637570</t>
+          <t>636759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1175896</t>
+          <t>1175702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1220364</t>
+          <t>1221498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26841</t>
+          <t>28892</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>22427</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>22075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44957</t>
+          <t>46804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>22286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>42275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39514</t>
+          <t>39577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51650</t>
+          <t>51807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68225</t>
+          <t>66378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91546</t>
+          <t>91107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94619</t>
+          <t>94525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>183173</t>
+          <t>186257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101871</t>
+          <t>102390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140215</t>
+          <t>139545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>210262</t>
+          <t>210981</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>310798</t>
+          <t>313897</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276521</t>
+          <t>273437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365075</t>
+          <t>365169</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>375697</t>
+          <t>376367</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>414041</t>
+          <t>413522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>664808</t>
+          <t>661709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>765344</t>
+          <t>764625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50823</t>
+          <t>51385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>36318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57737</t>
+          <t>58385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73119</t>
+          <t>74462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103254</t>
+          <t>101687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98728</t>
+          <t>98166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117734</t>
+          <t>116903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125612</t>
+          <t>124964</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147632</t>
+          <t>147031</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>229646</t>
+          <t>231213</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259781</t>
+          <t>258438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149245</t>
+          <t>147142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>253194</t>
+          <t>241548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162543</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206332</t>
+          <t>206571</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>323948</t>
+          <t>323126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>425635</t>
+          <t>421920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>407230</t>
+          <t>418876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>511179</t>
+          <t>513282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>554933</t>
+          <t>554694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>598722</t>
+          <t>601233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>996054</t>
+          <t>999769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1097741</t>
+          <t>1098563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP15-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP15-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14755</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27394</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>22047</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16046</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29507</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15677</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>28815</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,26%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14760</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27560</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,33%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32415</t>
+          <t>33454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51648</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66587</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59451</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72090</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>68820</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>61360</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>74821</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>62052</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>75190</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>75,74%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66587</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>59285</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72085</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,67%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126064</t>
+          <t>126383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145297</t>
+          <t>144258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>74864</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>102287</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>68771</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>94194</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>68275</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>94431</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,4%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>74998</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>101778</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149986</t>
+          <t>151194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187636</t>
+          <t>187720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>389322</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>374704</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>402127</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>506</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>335380</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>321893</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>347316</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>321656</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>347812</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>80,6%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>389322</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>375213</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>401993</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705442</t>
+          <t>705358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743092</t>
+          <t>741884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,07%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26283</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43815</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16082</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30968</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16414</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>29993</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>12,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>27444</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>44953</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>22,3%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47073</t>
+          <t>47500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70351</t>
+          <t>69043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>122872</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114323</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131855</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>77,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>83,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151515</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>143098</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>157984</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>144073</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>157652</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>87,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>122872</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>113185</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>130694</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>77,7%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>261854</t>
+          <t>263162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285132</t>
+          <t>284705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>126191</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>160127</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>110452</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>142934</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>109450</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>141613</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>18,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>127312</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>160443</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246113</t>
+          <t>246565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>294352</t>
+          <t>295760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>578781</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>561847</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>595783</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>828</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>555716</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>538087</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>570569</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>539408</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>571571</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>81,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>578781</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>561531</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>594662</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,17%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1108643</t>
+          <t>1107235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1156882</t>
+          <t>1156430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12380</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24993</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>23061</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17085</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30835</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16281</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29917</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,97%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12249</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>25153</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>32974</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52728</t>
+          <t>51671</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68085</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61199</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73812</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>78,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>71,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>69308</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>61534</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>75284</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>62452</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>76088</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>75,03%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,62%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68085</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61039</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73943</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>78,99%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125833</t>
+          <t>126890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145459</t>
+          <t>145587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86297</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>116872</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>75262</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>104555</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>75591</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>103907</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,51%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>87339</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>118317</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170822</t>
+          <t>171074</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208705</t>
+          <t>210488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>393412</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>377574</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>408149</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>363974</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>347655</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>376948</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>348303</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>376619</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>80,49%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>393412</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>376129</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>407107</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>79,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>737951</t>
+          <t>736168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>775834</t>
+          <t>775582</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30372</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>49380</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27855</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>45297</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>27798</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45906</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>31189</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>49854</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63368</t>
+          <t>63836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88573</t>
+          <t>89626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131296</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>121349</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140357</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>76,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>71,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>82,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>130408</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>121515</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>138957</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>120906</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>139014</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>131296</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>120875</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>139540</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>76,9%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248968</t>
+          <t>247915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>274173</t>
+          <t>273705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>170729</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>170729</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>170729</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>170729</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>170729</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>170729</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>139959</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>177942</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>130633</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>166963</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>129929</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>165279</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>142070</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>176875</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,1%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>278474</t>
+          <t>280199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>331695</t>
+          <t>331488</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>592793</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>573425</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>611408</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>812</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>563690</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>544428</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>580758</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>546112</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>581462</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>848</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>592793</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>574492</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>609297</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>78,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1131063</t>
+          <t>1131270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1184284</t>
+          <t>1182559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>751367</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>751367</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>751367</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>751367</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>751367</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>751367</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4884</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15069</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10804</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21634</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10955</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22173</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26,42%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4365</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13887</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>17295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33423</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59828</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53545</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63730</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43687</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>37744</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48574</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>37205</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48423</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>73,58%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>63,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59828</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>54727</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64249</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>87,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94570</t>
+          <t>95604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109996</t>
+          <t>110698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,64 +4272,64 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72518</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>98335</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>69872</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>95968</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>70076</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>96929</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>72523</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>99795</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,52%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>14,84%</t>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150491</t>
+          <t>153053</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>188253</t>
+          <t>189114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -4385,67 +4385,67 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>403115</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>390400</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>416217</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>389311</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>376322</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>402418</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>375361</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>402214</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>403115</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>388940</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>416212</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>82,48%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>772772</t>
+          <t>771911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810534</t>
+          <t>807972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21752</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38076</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22061</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37225</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21346</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>36987</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21112</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>37507</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47880</t>
+          <t>46690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71573</t>
+          <t>70103</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158625</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149419</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165743</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>143911</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>135478</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>150642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>135716</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>151357</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158625</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>149988</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166383</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>84,6%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>288624</t>
+          <t>290094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>312317</t>
+          <t>313507</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>106791</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>140198</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>111243</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>143709</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>110759</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>144834</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>18,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>108085</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>141931</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>227717</t>
+          <t>226261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273513</t>
+          <t>274110</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>621568</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>604646</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>638053</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>869</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>576910</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>560662</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>593128</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>559537</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>593612</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>81,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>886</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>621568</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>602913</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>636759</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1175702</t>
+          <t>1175105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221498</t>
+          <t>1222954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8886</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19589</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15229</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8903</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28892</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>29,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10197</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22075</t>
+          <t>17180</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46804</t>
+          <t>31237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42812</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37143</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47846</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>65,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>35949</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22286</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>42275</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>70,24%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>43,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46337</t>
+          <t>36110</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39577</t>
+          <t>31022</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51807</t>
+          <t>39868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>82285</t>
+          <t>78923</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66378</t>
+          <t>71387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91107</t>
+          <t>85444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>51178</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>51178</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51178</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45891</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45891</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>113182</t>
+          <t>102624</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113182</t>
+          <t>102624</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113182</t>
+          <t>102624</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>90853</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>125249</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>94525</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>186257</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>120023</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102390</t>
+          <t>78925</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139545</t>
+          <t>106105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>240866</t>
+          <t>200597</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>210981</t>
+          <t>180260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313897</t>
+          <t>226254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>367150</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>349813</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>384209</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>77,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>73,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>498</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>338851</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>273437</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>365169</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>79,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>395889</t>
+          <t>338918</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>376367</t>
+          <t>325497</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>413522</t>
+          <t>352677</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>734740</t>
+          <t>706067</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>661709</t>
+          <t>680410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>764625</t>
+          <t>726404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>975606</t>
+          <t>906664</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>975606</t>
+          <t>906664</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>975606</t>
+          <t>906664</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32661</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53872</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>32648</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51385</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,84%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36318</t>
+          <t>32057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58385</t>
+          <t>49773</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>70945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101687</t>
+          <t>98607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>125300</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114547</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>135758</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>74,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>80,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>107909</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>98166</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>116903</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>72,16%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>65,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>78,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>136838</t>
+          <t>109449</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124964</t>
+          <t>100203</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147031</t>
+          <t>117919</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>244747</t>
+          <t>234748</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>231213</t>
+          <t>219788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>258438</t>
+          <t>247450</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>143688</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>185319</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>147142</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>241548</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26,91%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160032</t>
+          <t>125497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206571</t>
+          <t>162084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>323126</t>
+          <t>282084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>421920</t>
+          <t>336288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>535261</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>514894</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>556525</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>482709</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>418876</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>513282</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73,09%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>77,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>579064</t>
+          <t>484477</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>554694</t>
+          <t>465385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>601233</t>
+          <t>501972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1061773</t>
+          <t>1019738</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>999769</t>
+          <t>991394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1098563</t>
+          <t>1045598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700213</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700213</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700213</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>660424</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>660424</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>660424</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761265</t>
+          <t>627469</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761265</t>
+          <t>627469</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761265</t>
+          <t>627469</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1421689</t>
+          <t>1327682</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1421689</t>
+          <t>1327682</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1421689</t>
+          <t>1327682</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
